--- a/projetos/OBRA_TMULT/07_DATABOOK_E_ASBUILT/CONTROLE_DATABOOK_CLOSEOUT_TMULT.xlsx
+++ b/projetos/OBRA_TMULT/07_DATABOOK_E_ASBUILT/CONTROLE_DATABOOK_CLOSEOUT_TMULT.xlsx
@@ -30,7 +30,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="15"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -84,20 +84,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF8FF"/>
-        <bgColor rgb="00EBF8FF"/>
+        <fgColor rgb="00E8EEF5"/>
+        <bgColor rgb="00E8EEF5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C5282"/>
-        <bgColor rgb="002C5282"/>
+        <fgColor rgb="00284B78"/>
+        <bgColor rgb="00284B78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6F6D5"/>
-        <bgColor rgb="00C6F6D5"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,13 +111,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="00DDDDDD"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="00DDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom style="medium">
         <color rgb="001A202C"/>
@@ -125,16 +125,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="00DDDDDD"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="00DDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E0"/>
+        <color rgb="00DDDDDD"/>
       </bottom>
     </border>
   </borders>
@@ -144,27 +144,27 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,13 +534,13 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="137" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -553,7 +553,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Empreendimento: TMULT — Terminal Multiuso (Porto do Açu) — Edifício Administrativo | Sistema PMO Virtual | Data de Emissão: 11/09/2026</t>
+          <t>Empreendimento: TMULT — Terminal Multiuso (Porto do Açu) — Edifício Administrativo | Sistema PMO Virtual | Data de Emissão: 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -854,14 +854,14 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
